--- a/appium-tests/reports/appium-test-report.xlsx
+++ b/appium-tests/reports/appium-test-report.xlsx
@@ -38,7 +38,7 @@
     <t>Platform &amp; Driver</t>
   </si>
   <si>
-    <t>Android / UiAutomator2 (Appium 2)</t>
+    <t>Android (UiAutomator2) on Windows 10.0.26300 (x64)</t>
   </si>
   <si>
     <t>API Base URL</t>
